--- a/data/between_importation_annee.xlsx
+++ b/data/between_importation_annee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -55,10 +55,19 @@
     <t>Air</t>
   </si>
   <si>
+    <t>Terrestre</t>
+  </si>
+  <si>
     <t>Douala</t>
   </si>
   <si>
+    <t>Brazzaville</t>
+  </si>
+  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Tradex</t>
   </si>
   <si>
     <t>Janvier</t>
@@ -423,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -475,10 +484,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -499,9 +508,50 @@
         <v>2000</v>
       </c>
       <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="M2">
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>10000</v>
+      </c>
+      <c r="G3">
+        <v>12500</v>
+      </c>
+      <c r="H3">
+        <v>11500</v>
+      </c>
+      <c r="I3">
+        <v>14500</v>
+      </c>
+      <c r="J3" s="2">
+        <v>36526</v>
+      </c>
+      <c r="K3">
+        <v>2000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>

--- a/data/between_importation_annee.xlsx
+++ b/data/between_importation_annee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -64,10 +64,16 @@
     <t>Brazzaville</t>
   </si>
   <si>
+    <t>Limbe</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
     <t>Tradex</t>
+  </si>
+  <si>
+    <t>Elf</t>
   </si>
   <si>
     <t>Janvier</t>
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -487,7 +493,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -508,7 +514,7 @@
         <v>2000</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -528,7 +534,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>10000</v>
@@ -549,9 +555,50 @@
         <v>2000</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>7500</v>
+      </c>
+      <c r="G4">
+        <v>6500</v>
+      </c>
+      <c r="H4">
+        <v>4500</v>
+      </c>
+      <c r="I4">
+        <v>9500</v>
+      </c>
+      <c r="J4" s="2">
+        <v>36526</v>
+      </c>
+      <c r="K4">
+        <v>2000</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>

--- a/data/between_importation_annee.xlsx
+++ b/data/between_importation_annee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -77,6 +77,21 @@
   </si>
   <si>
     <t>Janvier</t>
+  </si>
+  <si>
+    <t>Février</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>Aôut</t>
+  </si>
+  <si>
+    <t>Octobre</t>
+  </si>
+  <si>
+    <t>Novembre</t>
   </si>
 </sst>
 </file>
@@ -438,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -602,6 +617,252 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>3500</v>
+      </c>
+      <c r="G5">
+        <v>4500</v>
+      </c>
+      <c r="H5">
+        <v>6500</v>
+      </c>
+      <c r="I5">
+        <v>7500</v>
+      </c>
+      <c r="J5" s="2">
+        <v>36892</v>
+      </c>
+      <c r="K5">
+        <v>2001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>8500</v>
+      </c>
+      <c r="G6">
+        <v>6500</v>
+      </c>
+      <c r="H6">
+        <v>7500</v>
+      </c>
+      <c r="I6">
+        <v>9500</v>
+      </c>
+      <c r="J6" s="2">
+        <v>37288</v>
+      </c>
+      <c r="K6">
+        <v>2002</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>9800</v>
+      </c>
+      <c r="G7">
+        <v>7500</v>
+      </c>
+      <c r="H7">
+        <v>5600</v>
+      </c>
+      <c r="I7">
+        <v>10500</v>
+      </c>
+      <c r="J7" s="2">
+        <v>37799</v>
+      </c>
+      <c r="K7">
+        <v>2003</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>10600</v>
+      </c>
+      <c r="G8">
+        <v>8600</v>
+      </c>
+      <c r="H8">
+        <v>9800</v>
+      </c>
+      <c r="I8">
+        <v>10800</v>
+      </c>
+      <c r="J8" s="2">
+        <v>38218</v>
+      </c>
+      <c r="K8">
+        <v>2004</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9">
+        <v>15000</v>
+      </c>
+      <c r="G9">
+        <v>17600</v>
+      </c>
+      <c r="H9">
+        <v>10600</v>
+      </c>
+      <c r="I9">
+        <v>18000</v>
+      </c>
+      <c r="J9" s="2">
+        <v>38645</v>
+      </c>
+      <c r="K9">
+        <v>2005</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>7500</v>
+      </c>
+      <c r="G10">
+        <v>12500</v>
+      </c>
+      <c r="H10">
+        <v>9450</v>
+      </c>
+      <c r="I10">
+        <v>8250</v>
+      </c>
+      <c r="J10" s="2">
+        <v>39037</v>
+      </c>
+      <c r="K10">
+        <v>2006</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/between_importation_annee.xlsx
+++ b/data/between_importation_annee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -58,6 +58,9 @@
     <t>Terrestre</t>
   </si>
   <si>
+    <t>Fleuve</t>
+  </si>
+  <si>
     <t>Douala</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t>Limbe</t>
   </si>
   <si>
+    <t>Kinshasa</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
@@ -76,6 +82,12 @@
     <t>Elf</t>
   </si>
   <si>
+    <t>Green Oil</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
     <t>Janvier</t>
   </si>
   <si>
@@ -92,6 +104,15 @@
   </si>
   <si>
     <t>Novembre</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Mai</t>
+  </si>
+  <si>
+    <t>Septembre</t>
   </si>
 </sst>
 </file>
@@ -453,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -505,10 +526,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -529,7 +550,7 @@
         <v>2000</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -546,10 +567,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>10000</v>
@@ -570,7 +591,7 @@
         <v>2000</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -587,10 +608,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>7500</v>
@@ -611,7 +632,7 @@
         <v>2000</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -628,10 +649,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>3500</v>
@@ -652,7 +673,7 @@
         <v>2001</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -669,10 +690,10 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>8500</v>
@@ -693,7 +714,7 @@
         <v>2002</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -710,10 +731,10 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>9800</v>
@@ -734,7 +755,7 @@
         <v>2003</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -751,10 +772,10 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>10600</v>
@@ -775,7 +796,7 @@
         <v>2004</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M8">
         <v>8</v>
@@ -792,10 +813,10 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>15000</v>
@@ -816,7 +837,7 @@
         <v>2005</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -833,10 +854,10 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>7500</v>
@@ -857,10 +878,215 @@
         <v>2006</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M10">
         <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>9850</v>
+      </c>
+      <c r="G11">
+        <v>4500</v>
+      </c>
+      <c r="H11">
+        <v>8000</v>
+      </c>
+      <c r="I11">
+        <v>6250</v>
+      </c>
+      <c r="J11" s="2">
+        <v>39520</v>
+      </c>
+      <c r="K11">
+        <v>2008</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>9050</v>
+      </c>
+      <c r="G12">
+        <v>8500</v>
+      </c>
+      <c r="H12">
+        <v>7650</v>
+      </c>
+      <c r="I12">
+        <v>10500</v>
+      </c>
+      <c r="J12" s="2">
+        <v>39520</v>
+      </c>
+      <c r="K12">
+        <v>2008</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>5600</v>
+      </c>
+      <c r="G13">
+        <v>7600</v>
+      </c>
+      <c r="H13">
+        <v>10600</v>
+      </c>
+      <c r="I13">
+        <v>8600</v>
+      </c>
+      <c r="J13" s="2">
+        <v>39948</v>
+      </c>
+      <c r="K13">
+        <v>2009</v>
+      </c>
+      <c r="L13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14">
+        <v>10500</v>
+      </c>
+      <c r="G14">
+        <v>8000</v>
+      </c>
+      <c r="H14">
+        <v>9000</v>
+      </c>
+      <c r="I14">
+        <v>12500</v>
+      </c>
+      <c r="J14" s="2">
+        <v>40480</v>
+      </c>
+      <c r="K14">
+        <v>2010</v>
+      </c>
+      <c r="L14" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>6500</v>
+      </c>
+      <c r="G15">
+        <v>7500</v>
+      </c>
+      <c r="H15">
+        <v>8500</v>
+      </c>
+      <c r="I15">
+        <v>9500</v>
+      </c>
+      <c r="J15" s="2">
+        <v>41533</v>
+      </c>
+      <c r="K15">
+        <v>2013</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
